--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -162,6 +162,15 @@
   </si>
   <si>
     <t>游戏界面</t>
+  </si>
+  <si>
+    <t>Entity.EntityId</t>
+  </si>
+  <si>
+    <t>Cat</t>
+  </si>
+  <si>
+    <t>猫猫</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1366,6 +1375,23 @@
         <v>44</v>
       </c>
     </row>
+    <row r="15" spans="1:12">
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -86,79 +86,16 @@
     <t>注释</t>
   </si>
   <si>
-    <t>item.EQuality</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>最差品质</t>
-  </si>
-  <si>
-    <t>BLUE</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>PURPLE</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>紫色的</t>
-  </si>
-  <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>test.AccessFlag</t>
-  </si>
-  <si>
-    <t>WRITE</t>
-  </si>
-  <si>
-    <t>READ</t>
-  </si>
-  <si>
-    <t>TRUNCATE</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>READ_WRITE</t>
-  </si>
-  <si>
-    <t>WRITE|READ</t>
-  </si>
-  <si>
-    <t>位标记使用示例</t>
-  </si>
-  <si>
     <t>UIFormId</t>
   </si>
   <si>
-    <t>MainMenu</t>
+    <t>MenuForm</t>
   </si>
   <si>
     <t>主菜单</t>
   </si>
   <si>
-    <t>GameHUD</t>
+    <t>MainForm</t>
   </si>
   <si>
     <t>游戏界面</t>
@@ -1133,8 +1070,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1249,147 +1186,30 @@
       <c r="I4" t="s">
         <v>21</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
         <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:12">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="H14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="B15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>猫猫</t>
+  </si>
+  <si>
+    <t>GanTan</t>
+  </si>
+  <si>
+    <t>感叹号</t>
   </si>
 </sst>
 </file>
@@ -1070,8 +1076,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1212,6 +1218,14 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8" spans="1:12">
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>感叹号</t>
+  </si>
+  <si>
+    <t>Anger</t>
+  </si>
+  <si>
+    <t>愤怒</t>
   </si>
 </sst>
 </file>
@@ -1076,8 +1082,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1226,6 +1232,14 @@
         <v>28</v>
       </c>
     </row>
+    <row r="9" spans="1:12">
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="27930" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>游戏界面</t>
+  </si>
+  <si>
+    <t>SettingForm</t>
+  </si>
+  <si>
+    <t>设置界面</t>
   </si>
   <si>
     <t>Entity.EntityId</t>
@@ -127,10 +133,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -605,19 +611,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1082,8 +1088,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1207,37 +1213,45 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="B7" t="s">
+    <row r="6" spans="1:12">
+      <c r="H6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="I6" t="s">
         <v>25</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:12">
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
       <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" t="s">
         <v>29</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I10" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>愤怒</t>
+  </si>
+  <si>
+    <t>LightningBall</t>
+  </si>
+  <si>
+    <t>闪电球</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1254,6 +1260,14 @@
         <v>32</v>
       </c>
     </row>
+    <row r="12" spans="1:12">
+      <c r="H12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView windowWidth="25600" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>设置界面</t>
+  </si>
+  <si>
+    <t>GameOver</t>
+  </si>
+  <si>
+    <t>结束界面</t>
   </si>
   <si>
     <t>Entity.EntityId</t>
@@ -139,10 +145,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -617,19 +623,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1095,7 +1101,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1227,9 +1233,17 @@
         <v>25</v>
       </c>
     </row>
+    <row r="7" spans="1:12">
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="9" spans="1:12">
       <c r="B9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
@@ -1238,34 +1252,34 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="H10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="H11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="H12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
